--- a/Tong hop thon V sample.xlsx
+++ b/Tong hop thon V sample.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\ubnd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{832BAF80-3996-4723-8FF8-45E15751D2C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A9F1A5F-D98B-42A3-A157-FF2104DCF5BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14620" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="File tổng" sheetId="1" r:id="rId1"/>
-    <sheet name="check thong tin ho" sheetId="2" r:id="rId2"/>
+    <sheet name="mailing" sheetId="3" r:id="rId1"/>
+    <sheet name="File tổng" sheetId="1" r:id="rId2"/>
+    <sheet name="check thong tin ho" sheetId="2" r:id="rId3"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId3"/>
+    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_a1" localSheetId="1" hidden="1">{"'Sheet1'!$L$16"}</definedName>
+    <definedName name="_a1" localSheetId="2" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="_a1" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="_Fill" hidden="1">#REF!</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'check thong tin ho'!$A$1:$I$293</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'File tổng'!$A$1:$AE$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'check thong tin ho'!$A$1:$I$293</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'File tổng'!$A$1:$AE$83</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="_Order2" hidden="1">255</definedName>
     <definedName name="_Sort" hidden="1">#REF!</definedName>
@@ -38,10 +39,10 @@
     <definedName name="Cot.TDT.ĐSD">#REF!</definedName>
     <definedName name="Cot.TLTH">#REF!</definedName>
     <definedName name="DL.Tong">#REF!</definedName>
-    <definedName name="erge" localSheetId="1" hidden="1">{"'Sheet1'!$L$16"}</definedName>
+    <definedName name="erge" localSheetId="2" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="erge" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="HTML_CodePage" hidden="1">950</definedName>
-    <definedName name="HTML_Control" localSheetId="1" hidden="1">{"'Sheet1'!$L$16"}</definedName>
+    <definedName name="HTML_Control" localSheetId="2" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="HTML_Control" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="HTML_Description" hidden="1">""</definedName>
     <definedName name="HTML_Email" hidden="1">""</definedName>
@@ -55,13 +56,13 @@
     <definedName name="HTML_OS" hidden="1">0</definedName>
     <definedName name="HTML_PathFile" hidden="1">"C:\2689\Q\國內\00q3961台化龍德PTA3建造\MyHTML.htm"</definedName>
     <definedName name="HTML_Title" hidden="1">"00Q3961-SUM"</definedName>
-    <definedName name="huy" localSheetId="1" hidden="1">{"'Sheet1'!$L$16"}</definedName>
+    <definedName name="huy" localSheetId="2" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="huy" hidden="1">{"'Sheet1'!$L$16"}</definedName>
-    <definedName name="kl" localSheetId="1" hidden="1">{"'Sheet1'!$L$16"}</definedName>
+    <definedName name="kl" localSheetId="2" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="kl" hidden="1">{"'Sheet1'!$L$16"}</definedName>
-    <definedName name="thklcongd" localSheetId="1" hidden="1">{"'Sheet1'!$L$16"}</definedName>
+    <definedName name="thklcongd" localSheetId="2" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="thklcongd" hidden="1">{"'Sheet1'!$L$16"}</definedName>
-    <definedName name="THTKS" localSheetId="1" hidden="1">{"'Sheet1'!$L$16"}</definedName>
+    <definedName name="THTKS" localSheetId="2" hidden="1">{"'Sheet1'!$L$16"}</definedName>
     <definedName name="THTKS" hidden="1">{"'Sheet1'!$L$16"}</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -85,7 +86,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -107,7 +108,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="217">
   <si>
     <t>STT</t>
   </si>
@@ -574,6 +575,195 @@
   <si>
     <t>Lê Đức H</t>
   </si>
+  <si>
+    <t>chu dat</t>
+  </si>
+  <si>
+    <t>chu tai san</t>
+  </si>
+  <si>
+    <t>tong dien tich</t>
+  </si>
+  <si>
+    <t>TS1</t>
+  </si>
+  <si>
+    <t>TS2</t>
+  </si>
+  <si>
+    <t>TS3</t>
+  </si>
+  <si>
+    <t>TS4</t>
+  </si>
+  <si>
+    <t>TS5</t>
+  </si>
+  <si>
+    <t>TS6</t>
+  </si>
+  <si>
+    <t>TS7</t>
+  </si>
+  <si>
+    <t>CT1</t>
+  </si>
+  <si>
+    <t>CT2</t>
+  </si>
+  <si>
+    <t>CT3</t>
+  </si>
+  <si>
+    <t>CT4</t>
+  </si>
+  <si>
+    <t>CT5</t>
+  </si>
+  <si>
+    <t>SLTS1</t>
+  </si>
+  <si>
+    <t>SLTS2</t>
+  </si>
+  <si>
+    <t>SLTS3</t>
+  </si>
+  <si>
+    <t>SLTS4</t>
+  </si>
+  <si>
+    <t>SLTS5</t>
+  </si>
+  <si>
+    <t>SLTS6</t>
+  </si>
+  <si>
+    <t>SLTS7</t>
+  </si>
+  <si>
+    <t>SLCT1</t>
+  </si>
+  <si>
+    <t>SLCT2</t>
+  </si>
+  <si>
+    <t>SLCT3</t>
+  </si>
+  <si>
+    <t>SLCT4</t>
+  </si>
+  <si>
+    <t>SLCT5</t>
+  </si>
+  <si>
+    <t>Kích thước 45 cột x 1,5m. Nặng 100.17 kg</t>
+  </si>
+  <si>
+    <t>Kích thước 40m x 1 cái</t>
+  </si>
+  <si>
+    <t>Nặng 46.92 kg</t>
+  </si>
+  <si>
+    <t>Rộng 20m2</t>
+  </si>
+  <si>
+    <t>Loại 20cm ≤ đk gốc ≤ 30cm có 400 cây</t>
+  </si>
+  <si>
+    <t>Loại 12cm ≤ đk gốc &lt; 20cm có 825 cây</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn A; Lê Văn H</t>
+  </si>
+  <si>
+    <t>Lê Văn B; Lê Thị X</t>
+  </si>
+  <si>
+    <t>Quây tôn, cao &gt;3m, kết cấu thép mái lợp tôn, kích thước 3mx3m. Rộng 9m2</t>
+  </si>
+  <si>
+    <t>Kích thước 200x1,5m. Nặng 765kg</t>
+  </si>
+  <si>
+    <t>Nặng 160 Kg</t>
+  </si>
+  <si>
+    <t>Kích thước 2,5x2m. Nặng 30Kg</t>
+  </si>
+  <si>
+    <t>Kích thước 50m x 1cái</t>
+  </si>
+  <si>
+    <t>Dài 50m</t>
+  </si>
+  <si>
+    <t>Dài 120m</t>
+  </si>
+  <si>
+    <t>Rộng 100m2</t>
+  </si>
+  <si>
+    <t>Loại 4cm &lt; đk gốc ≤ 8cm có 100 cây</t>
+  </si>
+  <si>
+    <t>Loại 2cm &lt; đk gốc ≤ 4cm có 150 cây</t>
+  </si>
+  <si>
+    <t>Loại 7cm ≤ đk gốc &lt; 12cm có  16 cây</t>
+  </si>
+  <si>
+    <t>50% diện tích, tương đương 504m2</t>
+  </si>
+  <si>
+    <t>Nặng36 Kg</t>
+  </si>
+  <si>
+    <t>Kích thước 120x1,8m. Nặng 660.96kg</t>
+  </si>
+  <si>
+    <t>Loại 4cm &lt; đk gốc ≤ 8cm có 450 cây</t>
+  </si>
+  <si>
+    <t>Loại 2cm &lt; đk gốc ≤ 4cm có 382 cây</t>
+  </si>
+  <si>
+    <t>Loại 12cm ≤ đk gốc &lt; 20cm có 40 cây</t>
+  </si>
+  <si>
+    <t>Kích thước 0,1 x 1,5 x 40 cột. Tổng 0.6 m3</t>
+  </si>
+  <si>
+    <t>Dài 840m</t>
+  </si>
+  <si>
+    <t>Rộng 70m2</t>
+  </si>
+  <si>
+    <t>Kích thước 20cm ≤ đk gốc ≤ 30cm có 51.44 cây</t>
+  </si>
+  <si>
+    <t>Kích thước 20cm ≤ đk gốc ≤ 30cm có 15.432 cây</t>
+  </si>
+  <si>
+    <t>Kích thước đk gốc 20cm trở lên có 9 cây</t>
+  </si>
+  <si>
+    <t>Kích thước 0,1 x 0,1 x 1,5m x 77 cột. Tổng 1.155m3</t>
+  </si>
+  <si>
+    <t>Kích thước 1,5 x 240m. Nặng 918kg</t>
+  </si>
+  <si>
+    <t>Kích thước 12cm ≤ đk gốc &lt; 20cm có 36 cây</t>
+  </si>
+  <si>
+    <t>Kích thước 7cm ≤ đk gốc &lt; 12cm có 11.12 cây</t>
+  </si>
+  <si>
+    <t>Kích thước 7cm ≤ đk gốc &lt; 12cm có 14.136 cây</t>
+  </si>
 </sst>
 </file>
 
@@ -707,7 +897,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -748,6 +938,18 @@
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -875,7 +1077,7 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="182">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1392,6 +1594,30 @@
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1407,7 +1633,7 @@
     <cellStyle name="Percent 3" xfId="5" xr:uid="{D377DACF-620E-4961-990C-D5C8F17449A1}"/>
     <cellStyle name="Percent 4" xfId="7" xr:uid="{E3626243-BCDE-44F2-9F9C-8562C687242F}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1426,6 +1652,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -43179,10 +43415,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -43469,6 +43701,594 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BC9CB66-1FE9-4BE8-9688-1C06130B9AB1}">
+  <dimension ref="A1:AH7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="32" max="32" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:34" ht="45" x14ac:dyDescent="0.35">
+      <c r="A1" s="182" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="183" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="183" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="183" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="184" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1" s="183" t="s">
+        <v>110</v>
+      </c>
+      <c r="G1" s="183" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="185" t="s">
+        <v>157</v>
+      </c>
+      <c r="I1" s="185" t="s">
+        <v>158</v>
+      </c>
+      <c r="J1" s="185" t="s">
+        <v>159</v>
+      </c>
+      <c r="K1" s="185" t="s">
+        <v>160</v>
+      </c>
+      <c r="L1" s="185" t="s">
+        <v>161</v>
+      </c>
+      <c r="M1" s="185" t="s">
+        <v>162</v>
+      </c>
+      <c r="N1" s="185" t="s">
+        <v>163</v>
+      </c>
+      <c r="O1" s="186" t="s">
+        <v>164</v>
+      </c>
+      <c r="P1" s="186" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q1" s="186" t="s">
+        <v>166</v>
+      </c>
+      <c r="R1" s="186" t="s">
+        <v>167</v>
+      </c>
+      <c r="S1" s="186" t="s">
+        <v>168</v>
+      </c>
+      <c r="T1" s="187" t="s">
+        <v>169</v>
+      </c>
+      <c r="U1" s="187" t="s">
+        <v>170</v>
+      </c>
+      <c r="V1" s="187" t="s">
+        <v>171</v>
+      </c>
+      <c r="W1" s="187" t="s">
+        <v>172</v>
+      </c>
+      <c r="X1" s="187" t="s">
+        <v>173</v>
+      </c>
+      <c r="Y1" s="187" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z1" s="187" t="s">
+        <v>175</v>
+      </c>
+      <c r="AA1" s="188" t="s">
+        <v>176</v>
+      </c>
+      <c r="AB1" s="188" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC1" s="188" t="s">
+        <v>178</v>
+      </c>
+      <c r="AD1" s="188" t="s">
+        <v>179</v>
+      </c>
+      <c r="AE1" s="188" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF1" s="183" t="s">
+        <v>20</v>
+      </c>
+      <c r="AG1" s="183" t="s">
+        <v>21</v>
+      </c>
+      <c r="AH1" s="183" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:34" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>187</v>
+      </c>
+      <c r="C2" s="36" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="54"/>
+      <c r="E2" s="25">
+        <v>1596.4</v>
+      </c>
+      <c r="F2" s="25">
+        <v>50</v>
+      </c>
+      <c r="G2" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="K2" s="8"/>
+      <c r="O2" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q2" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA2" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC2" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="AF2" s="17">
+        <v>671559</v>
+      </c>
+      <c r="AG2" s="17">
+        <v>93645000</v>
+      </c>
+      <c r="AH2" s="17">
+        <f>SUM(AF2:AG2)</f>
+        <v>94316559</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" ht="62" x14ac:dyDescent="0.35">
+      <c r="A3" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="189" t="s">
+        <v>188</v>
+      </c>
+      <c r="C3" s="36" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="122"/>
+      <c r="E3" s="55">
+        <v>1200</v>
+      </c>
+      <c r="F3" s="55">
+        <v>50</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="8"/>
+      <c r="O3" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="R3" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="T3" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="U3" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="V3" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="W3" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="X3" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y3" s="12"/>
+      <c r="AA3" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="AB3" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="AC3" s="59" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD3" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="AF3" s="17">
+        <v>4151892</v>
+      </c>
+      <c r="AG3" s="17">
+        <v>285350000</v>
+      </c>
+      <c r="AH3" s="17">
+        <f>SUM(AF3:AG3)</f>
+        <v>289501892</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" ht="155" x14ac:dyDescent="0.35">
+      <c r="A4" s="55">
+        <v>89</v>
+      </c>
+      <c r="B4" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="D4" s="122">
+        <v>2880</v>
+      </c>
+      <c r="E4" s="55">
+        <v>1008</v>
+      </c>
+      <c r="F4" s="55">
+        <v>50</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="N4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="P4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="R4" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="U4" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="V4" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="W4" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="X4" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="Y4" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z4" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="AA4" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="AB4" s="59" t="s">
+        <v>197</v>
+      </c>
+      <c r="AC4" s="59" t="s">
+        <v>198</v>
+      </c>
+      <c r="AD4" s="59" t="s">
+        <v>199</v>
+      </c>
+      <c r="AE4" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="AF4" s="17">
+        <v>3706388</v>
+      </c>
+      <c r="AG4" s="17">
+        <v>35390000</v>
+      </c>
+      <c r="AH4" s="17">
+        <v>39096388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" ht="93" x14ac:dyDescent="0.35">
+      <c r="A5" s="55">
+        <v>2</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="C5" s="36" t="s">
+        <v>131</v>
+      </c>
+      <c r="D5" s="122"/>
+      <c r="E5" s="55">
+        <v>1000</v>
+      </c>
+      <c r="F5" s="55">
+        <v>50</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="8"/>
+      <c r="O5" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="P5" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q5" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="T5" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="U5" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="V5" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="W5" s="12"/>
+      <c r="AA5" s="59" t="s">
+        <v>203</v>
+      </c>
+      <c r="AB5" s="59" t="s">
+        <v>204</v>
+      </c>
+      <c r="AC5" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="AF5" s="17">
+        <v>2138041</v>
+      </c>
+      <c r="AG5" s="17">
+        <v>101600000</v>
+      </c>
+      <c r="AH5" s="17">
+        <v>103738041</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="94.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="55">
+        <v>59</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="D6" s="122">
+        <v>2880</v>
+      </c>
+      <c r="E6" s="55">
+        <v>1356</v>
+      </c>
+      <c r="F6" s="55">
+        <v>50</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="O6" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="P6" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q6" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="R6" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="T6" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="U6" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="V6" s="12"/>
+      <c r="AA6" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB6" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="AC6" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="AD6" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="AF6" s="17">
+        <v>1570913</v>
+      </c>
+      <c r="AG6" s="17">
+        <v>115378980</v>
+      </c>
+      <c r="AH6" s="17">
+        <v>116949893</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="55">
+        <v>133</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="122">
+        <v>2880</v>
+      </c>
+      <c r="E7" s="55">
+        <v>1248</v>
+      </c>
+      <c r="F7" s="55">
+        <v>50</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="I7" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="8"/>
+      <c r="O7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="P7" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q7" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="T7" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="U7" s="12" t="s">
+        <v>213</v>
+      </c>
+      <c r="V7" s="12"/>
+      <c r="AA7" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="AB7" s="59" t="s">
+        <v>214</v>
+      </c>
+      <c r="AC7" s="59" t="s">
+        <v>215</v>
+      </c>
+      <c r="AD7" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="AF7" s="17">
+        <v>2575861</v>
+      </c>
+      <c r="AG7" s="17">
+        <v>95448800</v>
+      </c>
+      <c r="AH7" s="17">
+        <v>98024661</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1">
+    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:AE83"/>
@@ -43618,7 +44438,9 @@
       <c r="K2" s="64"/>
       <c r="L2" s="64"/>
       <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
+      <c r="N2" s="64">
+        <v>1</v>
+      </c>
       <c r="O2" s="64"/>
       <c r="P2" s="131"/>
       <c r="Q2" s="154"/>
@@ -45190,7 +46012,7 @@
       <c r="G33" s="12"/>
       <c r="H33" s="81"/>
       <c r="I33" s="19"/>
-      <c r="J33" s="14"/>
+      <c r="J33" s="19"/>
       <c r="K33" s="12" t="s">
         <v>63</v>
       </c>
@@ -45247,7 +46069,9 @@
       <c r="K34" s="64"/>
       <c r="L34" s="64"/>
       <c r="M34" s="64"/>
-      <c r="N34" s="64"/>
+      <c r="N34" s="64">
+        <v>2</v>
+      </c>
       <c r="O34" s="64"/>
       <c r="P34" s="131"/>
       <c r="Q34" s="154"/>
@@ -46610,7 +47434,9 @@
       <c r="K61" s="64"/>
       <c r="L61" s="64"/>
       <c r="M61" s="64"/>
-      <c r="N61" s="64"/>
+      <c r="N61" s="64">
+        <v>3</v>
+      </c>
       <c r="O61" s="64"/>
       <c r="P61" s="131"/>
       <c r="Q61" s="154"/>
@@ -47740,7 +48566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77976C67-95C4-4268-9FAB-CB1B21D9B539}">
   <dimension ref="A1:V883"/>
   <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="34" customHeight="1" x14ac:dyDescent="0.35"/>
